--- a/bokslut2025/balans-rapport-bokio.xlsx
+++ b/bokslut2025/balans-rapport-bokio.xlsx
@@ -103,7 +103,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>Källa: sie4-export.se · Genererad: 2026-09-30T20:25:07+02:00</t>
+          <t>Källa: sie4-2025.se · Genererad: 2026-09-30T20:43:09+02:00</t>
         </is>
       </c>
     </row>

--- a/bokslut2025/balans-rapport-bokio.xlsx
+++ b/bokslut2025/balans-rapport-bokio.xlsx
@@ -96,14 +96,14 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>Räkenskapsår: 20250501–20260430 · Senaste verifikation: V99</t>
+          <t>Räkenskapsår: 20250501–20260430 · Senaste verifikation: V101</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>Källa: sie4-2025.se · Genererad: 2026-09-30T20:43:09+02:00</t>
+          <t>Källa: sie4-2025.se · Genererad: 2026-09-30T22:16:31+02:00</t>
         </is>
       </c>
     </row>
